--- a/order_forms/040_stock_certificate_delivery_form--order_forms.xlsx
+++ b/order_forms/040_stock_certificate_delivery_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'9-1',_'value':_'california'}</t>
+          <t>california</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '9-1', 'value': 'California'}</t>
+          <t>California</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'9-2',_'value':_'new_york'}</t>
+          <t>new_york</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '9-2', 'value': 'New York'}</t>
+          <t>New York</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'9-3',_'value':_'texas'}</t>
+          <t>texas</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '9-3', 'value': 'Texas'}</t>
+          <t>Texas</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'18-1',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '18-1', 'value': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'18-2',_'value':_'mail'}</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '18-2', 'value': 'Mail'}</t>
+          <t>Mail</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'20-1',_'value':_'issued'}</t>
+          <t>issued</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '20-1', 'value': 'Issued'}</t>
+          <t>Issued</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'20-2',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '20-2', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'20-3',_'value':_'voided'}</t>
+          <t>voided</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '20-3', 'value': 'Voided'}</t>
+          <t>Voided</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'21-1',_'value':_'delivered'}</t>
+          <t>delivered</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '21-1', 'value': 'Delivered'}</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'21-2',_'value':_'not_delivered'}</t>
+          <t>not_delivered</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '21-2', 'value': 'Not Delivered'}</t>
+          <t>Not Delivered</t>
         </is>
       </c>
     </row>
